--- a/Input_data/IST_US_trad_eco_cal_2025-02-14_to_2025-02-26.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-02-14_to_2025-02-26.xlsx
@@ -490,26 +490,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -520,22 +520,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -546,22 +550,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.9%</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>-0.8%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -572,26 +580,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.3%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>2.7%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -602,18 +606,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -628,26 +632,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.8%</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>1.9%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -658,26 +658,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>-0.5%</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -688,26 +684,26 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -718,22 +714,26 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>1.3%</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -1512,7 +1512,11 @@
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>$149.1B</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="n">
         <v>2</v>
@@ -1566,14 +1570,14 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -1656,7 +1660,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -1674,14 +1678,14 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -1710,7 +1714,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -1728,7 +1732,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -1746,18 +1750,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>1.39M</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -1868,14 +1876,14 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -1890,22 +1898,18 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>1.39M</t>
-        </is>
-      </c>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -2384,7 +2388,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -2402,14 +2406,22 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F93" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
@@ -2420,7 +2432,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -2438,22 +2450,14 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
       <c r="F95" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96">
@@ -2464,12 +2468,16 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F96" t="n">
         <v>3</v>
       </c>
@@ -2500,18 +2508,22 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99">
@@ -2544,22 +2556,14 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
       <c r="F100" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="101">
@@ -2694,7 +2698,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -2712,7 +2716,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -2766,7 +2770,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -2784,7 +2788,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
@@ -2802,14 +2806,14 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="114">
@@ -2820,14 +2824,14 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="115">
@@ -2838,7 +2842,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -2856,14 +2860,14 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117">
@@ -2874,14 +2878,14 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118">
@@ -2892,7 +2896,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -2910,7 +2914,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -2928,7 +2932,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -2946,7 +2950,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -3342,11 +3346,15 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>53.2</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>52.7</t>
@@ -3364,14 +3372,14 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F144" t="n">
@@ -3386,14 +3394,14 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F145" t="n">
@@ -3634,18 +3642,22 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
-      <c r="D155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>4.17M</t>
+        </is>
+      </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156">
@@ -3656,22 +3668,22 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
         <is>
-          <t>4.17M</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="157">
@@ -3682,22 +3694,22 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="158">
@@ -3708,18 +3720,18 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F158" t="n">
@@ -3734,22 +3746,18 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>67.3</t>
-        </is>
-      </c>
+      <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160">
@@ -3760,18 +3768,18 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F160" t="n">
@@ -4014,7 +4022,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
@@ -4068,7 +4076,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
@@ -4212,14 +4220,18 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr"/>
-      <c r="E184" t="inlineStr"/>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F184" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="185">
@@ -4230,7 +4242,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
@@ -4248,7 +4260,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
@@ -4288,7 +4300,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
@@ -4324,18 +4336,14 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr"/>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E190" t="inlineStr"/>
       <c r="F190" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="191">
@@ -4418,14 +4426,14 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="196">
@@ -4436,7 +4444,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
@@ -4454,7 +4462,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
@@ -4472,14 +4480,14 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="199">
@@ -4562,7 +4570,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C203" t="inlineStr"/>
@@ -4580,7 +4588,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
